--- a/publish/StructureDefinition-no-domain-VitalSigns-Observation-bloodpressure.xlsx
+++ b/publish/StructureDefinition-no-domain-VitalSigns-Observation-bloodpressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -390,7 +390,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -641,7 +641,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -670,7 +670,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -750,7 +750,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1040,7 +1040,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1165,7 +1165,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1188,7 +1188,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1287,7 +1287,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1400,7 +1400,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1432,7 +1432,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1551,7 +1551,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1579,7 +1579,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1659,7 +1659,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1709,7 +1709,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1745,7 +1745,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1782,7 +1782,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1804,7 +1804,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -5505,7 +5505,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>214</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>237</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>252</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>266</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>284</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>320</v>
       </c>
@@ -8761,7 +8761,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>358</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>385</v>
       </c>
@@ -9849,7 +9849,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>434</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>436</v>
       </c>
@@ -13697,7 +13697,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>587</v>
       </c>
@@ -13819,7 +13819,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
         <v>593</v>
       </c>
@@ -13941,7 +13941,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>602</v>
       </c>
@@ -14307,7 +14307,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>611</v>
       </c>
@@ -14791,7 +14791,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>617</v>
       </c>
@@ -17325,7 +17325,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
         <v>657</v>
       </c>
@@ -17685,7 +17685,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
         <v>662</v>
       </c>
@@ -17929,7 +17929,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>683</v>
       </c>
@@ -18049,7 +18049,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
         <v>691</v>
       </c>
@@ -18169,7 +18169,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
         <v>700</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
         <v>708</v>
       </c>
@@ -18657,7 +18657,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
         <v>711</v>
       </c>
@@ -19141,7 +19141,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="135" hidden="true">
+    <row r="135">
       <c r="A135" t="s" s="2">
         <v>717</v>
       </c>
@@ -21675,7 +21675,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>744</v>
       </c>
@@ -22035,7 +22035,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="159" hidden="true">
+    <row r="159">
       <c r="A159" t="s" s="2">
         <v>747</v>
       </c>
@@ -22279,7 +22279,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
         <v>749</v>
       </c>
@@ -22399,7 +22399,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="162" hidden="true">
+    <row r="162">
       <c r="A162" t="s" s="2">
         <v>750</v>
       </c>
@@ -22519,7 +22519,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
         <v>751</v>
       </c>
@@ -22641,7 +22641,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="164" hidden="true">
+    <row r="164">
       <c r="A164" t="s" s="2">
         <v>752</v>
       </c>
@@ -23007,7 +23007,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="167" hidden="true">
+    <row r="167">
       <c r="A167" t="s" s="2">
         <v>755</v>
       </c>
@@ -23491,7 +23491,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
         <v>762</v>
       </c>
@@ -26025,7 +26025,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="192" hidden="true">
+    <row r="192">
       <c r="A192" t="s" s="2">
         <v>791</v>
       </c>
@@ -26991,7 +26991,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="200" hidden="true">
+    <row r="200">
       <c r="A200" t="s" s="2">
         <v>801</v>
       </c>
@@ -27357,7 +27357,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="203" hidden="true">
+    <row r="203">
       <c r="A203" t="s" s="2">
         <v>804</v>
       </c>
@@ -27841,7 +27841,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="207" hidden="true">
+    <row r="207">
       <c r="A207" t="s" s="2">
         <v>810</v>
       </c>
@@ -29409,7 +29409,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="220" hidden="true">
+    <row r="220">
       <c r="A220" t="s" s="2">
         <v>826</v>
       </c>
@@ -30375,7 +30375,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="228" hidden="true">
+    <row r="228">
       <c r="A228" t="s" s="2">
         <v>834</v>
       </c>
@@ -30743,12 +30743,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP230">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/publish/StructureDefinition-no-domain-VitalSigns-Observation-bloodpressure.xlsx
+++ b/publish/StructureDefinition-no-domain-VitalSigns-Observation-bloodpressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/publish/StructureDefinition-no-domain-VitalSigns-Observation-bloodpressure.xlsx
+++ b/publish/StructureDefinition-no-domain-VitalSigns-Observation-bloodpressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
